--- a/results/log_pv_cap/log_pv_cap_densities_adensity_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_adensity_effects.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>adensity</t>
+          <t>D(Firm assets)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -608,291 +608,291 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.208</t>
+          <t>7.382</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.513</t>
+          <t>-0.044</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.722</t>
+          <t>7.426</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.518</t>
+          <t>5.309</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.075</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.593</t>
+          <t>4.913</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>5.065</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.248</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-2.025</t>
+          <t>1.749</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.382</t>
+          <t>1.058</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-1.643</t>
+          <t>0.690</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.141</t>
+          <t>4.129</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.054</t>
+          <t>3.797</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.466</t>
+          <t>4.318</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.822</t>
+          <t>4.185</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.133</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.302</t>
+          <t>-0.396</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.431</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.161</t>
+          <t>0.557</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.935</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.357</t>
+          <t>-0.418</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.326</t>
+          <t>-0.363</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.154</t>
+          <t>-0.196</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.115</t>
+          <t>-0.141</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.228</t>
+          <t>-0.257</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.209</t>
+          <t>-0.197</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.085</t>
+          <t>-0.119</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.072</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.047</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.112</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.096</t>
+          <t>-0.127</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.078</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.004</t>
         </is>
       </c>
     </row>
